--- a/site/exports/sysu-math.xlsx
+++ b/site/exports/sysu-math.xlsx
@@ -452,7 +452,7 @@
     <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
     <col width="44.8" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
